--- a/ENGLISH_timetable.xlsx
+++ b/ENGLISH_timetable.xlsx
@@ -613,7 +613,11 @@
           <t>6E ENGLISH</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10B ENGLISH</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>8B ENGLISH</t>
@@ -691,14 +695,10 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10B ENGLISH</t>
-        </is>
-      </c>
+          <t>6B ENGLISH</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7A ENGLISH</t>
@@ -747,17 +747,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6D S.ST</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>7D ENGLISH</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6D S.ST</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6B ENGLISH</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6B ENGLISH</t>
+          <t>7D ENGLISH</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -916,11 +916,7 @@
           <t>10:10-10:50</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>7D ENGLISH</t>
-        </is>
-      </c>
+      <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -966,17 +962,17 @@
           <t>11:20-12:00</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>6C ENGLISH</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1042,7 +1038,11 @@
           <t>6D ENGLISH</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>6B ENGLISH</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>9A ENGLISH</t>
@@ -1263,11 +1263,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>9A ENGLISH</t>
@@ -1364,11 +1360,15 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>7D ENGLISH</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>10E ENGLISH</t>
@@ -1498,17 +1498,17 @@
           <t>10:40-11:15</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>7B ENGLISH</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
+      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>9A ENGLISH</t>
@@ -1601,7 +1601,11 @@
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>7D ENGLISH</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>10E ENGLISH</t>
@@ -1653,11 +1657,7 @@
           <t>1:15-2:00</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>7D ENGLISH</t>
-        </is>
-      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>6D ENGLISH</t>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>7D ENGLISH</t>
+          <t>8C ENGLISH</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1861,7 +1861,11 @@
           <t>8A ENGLISH</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>7D ENGLISH</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
@@ -1888,11 +1892,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
+      <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>9D ENGLISH</t>

--- a/ENGLISH_timetable.xlsx
+++ b/ENGLISH_timetable.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -434,6 +434,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,6 +512,11 @@
           <t>AMINA NADEEM</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>LUBNA TARIQ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -549,11 +555,8 @@
           <t>9E ENGLISH</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9B ENGLISH</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
@@ -568,27 +571,24 @@
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7B ENGLISH</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9D ENGLISH</t>
+          <t>10E ENGLISH</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9F ENGLISH</t>
+          <t>7A ENGLISH</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10F ENGLISH</t>
-        </is>
-      </c>
+          <t>10D ENGLISH</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr"/>
@@ -602,28 +602,21 @@
           <t>9:30-10:10</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10C ENGLISH</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>6E ENGLISH</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>10B ENGLISH</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>8B ENGLISH</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7B ENGLISH</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9B ENGLISH</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
@@ -637,24 +630,29 @@
           <t>10:10-10:50</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10C ENGLISH</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6D ENGLISH</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
+          <t>6D S.ST</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6B ENGLISH</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10E ENGLISH</t>
+          <t>10B ENGLISH</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7C S.ST</t>
-        </is>
-      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr"/>
@@ -670,6 +668,7 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr"/>
@@ -683,32 +682,21 @@
           <t>11:20-12:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9C ENGLISH</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6C ENGLISH</t>
-        </is>
-      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6B ENGLISH</t>
+          <t>6E ENGLISH</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7A ENGLISH</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10A ENGLISH</t>
-        </is>
-      </c>
+          <t>7C ENGLISH</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
@@ -722,16 +710,25 @@
           <t>12:00-12:40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7B S.ST</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9C ENGLISH</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6D ENGLISH</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9A ENGLISH</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr"/>
@@ -750,11 +747,7 @@
           <t>8C ENGLISH</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6D S.ST</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>7D ENGLISH</t>
@@ -762,11 +755,20 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8A Geography</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>8E ENGLISH</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8B ENGLISH</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10A ENGLISH</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr"/>
@@ -785,23 +787,28 @@
           <t>6A ENGLISH</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>9A ENGLISH</t>
-        </is>
-      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6C ENGLISH</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7B S.ST</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7C ENGLISH</t>
+          <t>9F ENGLISH</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10D ENGLISH</t>
-        </is>
-      </c>
+          <t>10F ENGLISH</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -835,8 +842,13 @@
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9E ENGLISH</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr"/>
@@ -851,27 +863,16 @@
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7B ENGLISH</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7D ENGLISH</t>
-        </is>
-      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9F ENGLISH</t>
-        </is>
-      </c>
+      <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10A ENGLISH</t>
-        </is>
-      </c>
+          <t>10F ENGLISH</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
@@ -890,19 +891,28 @@
           <t>6A ENGLISH</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6C ENGLISH</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6B ENGLISH</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>10E ENGLISH</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10D ENGLISH</t>
-        </is>
-      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7A ENGLISH</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr"/>
@@ -916,24 +926,29 @@
           <t>10:10-10:50</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10C ENGLISH</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7B S.ST</t>
+          <t>7D ENGLISH</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10B ENGLISH</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8B ENGLISH</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>8E ENGLISH</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7C S.ST</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr"/>
@@ -949,6 +964,7 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr"/>
@@ -962,28 +978,29 @@
           <t>11:20-12:00</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
+      <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6C ENGLISH</t>
+          <t>6D ENGLISH</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>10B ENGLISH</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7A ENGLISH</t>
+          <t>7C ENGLISH</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10F ENGLISH</t>
-        </is>
-      </c>
+          <t>9B ENGLISH</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr"/>
@@ -997,24 +1014,29 @@
           <t>12:00-12:40</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>6D S.ST</t>
-        </is>
-      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9C ENGLISH</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9D ENGLISH</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>9A ENGLISH</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9F ENGLISH</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7C S.ST</t>
-        </is>
-      </c>
+          <t>10D ENGLISH</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr"/>
@@ -1030,30 +1052,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10C ENGLISH</t>
+          <t>8C ENGLISH</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6D ENGLISH</t>
+          <t>6D S.ST</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6B ENGLISH</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>9A ENGLISH</t>
-        </is>
-      </c>
+          <t>7B S.ST</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7C ENGLISH</t>
+          <t>8B ENGLISH</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
@@ -1067,28 +1086,25 @@
           <t>1:20-2:00</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>9C ENGLISH</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>7B ENGLISH</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>6E ENGLISH</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>9E ENGLISH</t>
-        </is>
-      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9B ENGLISH</t>
-        </is>
-      </c>
+          <t>10A ENGLISH</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1128,6 +1144,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr"/>
@@ -1141,12 +1158,12 @@
           <t>8:50-9:30</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>6D S.ST</t>
-        </is>
-      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>7B S.ST</t>
@@ -1154,19 +1171,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8A Geography</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>9F ENGLISH</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>7C S.ST</t>
-        </is>
-      </c>
+          <t>8E ENGLISH</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr"/>
@@ -1180,28 +1190,25 @@
           <t>9:30-10:10</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>9C ENGLISH</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>6B ENGLISH</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>10B ENGLISH</t>
-        </is>
-      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>6D S.ST</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7C ENGLISH</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t>7A ENGLISH</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>10D ENGLISH</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr"/>
@@ -1218,17 +1225,26 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6D ENGLISH</t>
+          <t>7B ENGLISH</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>9A ENGLISH</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>9F ENGLISH</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10A ENGLISH</t>
-        </is>
-      </c>
+          <t>7C S.ST</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr"/>
@@ -1244,6 +1260,7 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr"/>
@@ -1259,26 +1276,23 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10C ENGLISH</t>
+          <t>6A ENGLISH</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>7D ENGLISH</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9A ENGLISH</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>7A ENGLISH</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>10F ENGLISH</t>
-        </is>
-      </c>
+          <t>8A Geography</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr"/>
@@ -1292,28 +1306,33 @@
           <t>12:00-12:40</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10C ENGLISH</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7B ENGLISH</t>
+          <t>6C ENGLISH</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9D ENGLISH</t>
+          <t>10E ENGLISH</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8B ENGLISH</t>
+          <t>7C ENGLISH</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9B ENGLISH</t>
-        </is>
-      </c>
+          <t>10F ENGLISH</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr"/>
@@ -1327,14 +1346,10 @@
           <t>12:40-1:20</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>6A ENGLISH</t>
-        </is>
-      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6C ENGLISH</t>
+          <t>6D ENGLISH</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1344,7 +1359,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>9B ENGLISH</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr"/>
@@ -1360,30 +1380,31 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8C ENGLISH</t>
+          <t>9C ENGLISH</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7D ENGLISH</t>
+          <t>6B ENGLISH</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10E ENGLISH</t>
+          <t>10B ENGLISH</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9F ENGLISH</t>
+          <t>8B ENGLISH</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10D ENGLISH</t>
-        </is>
-      </c>
+          <t>10A ENGLISH</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1422,11 +1443,8 @@
           <t>9E ENGLISH</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>9B ENGLISH</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr"/>
@@ -1448,20 +1466,25 @@
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6E ENGLISH</t>
+          <t>7B S.ST</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8A Geography</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
+          <t>9A ENGLISH</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>7A ENGLISH</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
           <t>10F ENGLISH</t>
         </is>
       </c>
+      <c r="J35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr"/>
@@ -1476,15 +1499,24 @@
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>6C ENGLISH</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>7D ENGLISH</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8B ENGLISH</t>
+          <t>7C ENGLISH</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr"/>
@@ -1498,32 +1530,21 @@
           <t>10:40-11:15</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>7B ENGLISH</t>
-        </is>
-      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9A ENGLISH</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>7A ENGLISH</t>
-        </is>
-      </c>
+          <t>10B ENGLISH</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7C S.ST</t>
-        </is>
-      </c>
+          <t>9B ENGLISH</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr"/>
@@ -1539,6 +1560,7 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr"/>
@@ -1554,34 +1576,23 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10C ENGLISH</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>6C ENGLISH</t>
-        </is>
-      </c>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7B S.ST</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>10B ENGLISH</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>7C ENGLISH</t>
-        </is>
-      </c>
+          <t>6E ENGLISH</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
           <t>10D ENGLISH</t>
         </is>
       </c>
+      <c r="J39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr"/>
@@ -1595,17 +1606,13 @@
           <t>12:10-12:45</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>6A ENGLISH</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>7D ENGLISH</t>
-        </is>
-      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>7B ENGLISH</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>10E ENGLISH</t>
@@ -1617,6 +1624,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr"/>
@@ -1630,20 +1638,33 @@
           <t>12:45-1:15</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10C ENGLISH</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6D S.ST</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+          <t>6D ENGLISH</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>6B ENGLISH</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>8E ENGLISH</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t>10A ENGLISH</t>
         </is>
       </c>
+      <c r="J41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr"/>
@@ -1657,24 +1678,33 @@
           <t>1:15-2:00</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>6A ENGLISH</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6D ENGLISH</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>6B ENGLISH</t>
-        </is>
-      </c>
+          <t>6D S.ST</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>9D ENGLISH</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>8A Geography</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>8B ENGLISH</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>7C S.ST</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1692,24 +1722,33 @@
           <t>8:00-8:40</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>10C ENGLISH</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>6D ENGLISH</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7E ENGLISH</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
+          <t>6B ENGLISH</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>8E ENGLISH</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9E ENGLISH</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+          <t>7C ENGLISH</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>10A ENGLISH</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr"/>
@@ -1723,20 +1762,29 @@
           <t>8:40-9:15</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>9C ENGLISH</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6C ENGLISH</t>
+          <t>8A ENGLISH</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>10E ENGLISH</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
+          <t>10B ENGLISH</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>7A ENGLISH</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr"/>
@@ -1752,7 +1800,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>8C ENGLISH</t>
+          <t>6A ENGLISH</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1762,24 +1810,17 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>6B ENGLISH</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>9A ENGLISH</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>7C ENGLISH</t>
-        </is>
-      </c>
+          <t>7D ENGLISH</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10A ENGLISH</t>
-        </is>
-      </c>
+          <t>9B ENGLISH</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr"/>
@@ -1795,22 +1836,14 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>6A ENGLISH</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>6D ENGLISH</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>6E ENGLISH</t>
-        </is>
-      </c>
+          <t>10C ENGLISH</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>10B ENGLISH</t>
+          <t>10E ENGLISH</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -1820,9 +1853,10 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9B ENGLISH</t>
-        </is>
-      </c>
+          <t>10F ENGLISH</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr"/>
@@ -1838,6 +1872,7 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr"/>
@@ -1853,26 +1888,31 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>8D ENGLISH</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>8A ENGLISH</t>
-        </is>
-      </c>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>7D ENGLISH</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
+          <t>7E ENGLISH</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>9A ENGLISH</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>9F ENGLISH</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10F ENGLISH</t>
-        </is>
-      </c>
+          <t>7C S.ST</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr"/>
@@ -1888,19 +1928,27 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>9C ENGLISH</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
+          <t>8D ENGLISH</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>6C ENGLISH</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>6E ENGLISH</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>9D ENGLISH</t>
+          <t>8A Geography</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>7A ENGLISH</t>
+          <t>9E ENGLISH</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -1908,13 +1956,14 @@
           <t>10D ENGLISH</t>
         </is>
       </c>
+      <c r="J49" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
